--- a/Assets/_OriginalData/Excel/Config/Common/Prop.xlsx
+++ b/Assets/_OriginalData/Excel/Config/Common/Prop.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="87">
   <si>
     <t>ID</t>
   </si>
@@ -68,6 +68,9 @@
     <t>Prop_RemoveAD</t>
   </si>
   <si>
+    <t>移除广告</t>
+  </si>
+  <si>
     <t>Energy</t>
   </si>
   <si>
@@ -77,6 +80,9 @@
     <t>Prop_Energy</t>
   </si>
   <si>
+    <t>体力</t>
+  </si>
+  <si>
     <t>Coin</t>
   </si>
   <si>
@@ -86,6 +92,9 @@
     <t>Prop_Coin</t>
   </si>
   <si>
+    <t>金币</t>
+  </si>
+  <si>
     <t>ScrewExtraSlot</t>
   </si>
   <si>
@@ -95,6 +104,9 @@
     <t>Prop_ScrewExtraSlot</t>
   </si>
   <si>
+    <t>额外槽</t>
+  </si>
+  <si>
     <t>ScrewHammer</t>
   </si>
   <si>
@@ -104,6 +116,9 @@
     <t>Prop_ScrewHammer</t>
   </si>
   <si>
+    <t>锤子</t>
+  </si>
+  <si>
     <t>ScrewExtraBox</t>
   </si>
   <si>
@@ -113,6 +128,9 @@
     <t>Prop_ScrewExtraBox</t>
   </si>
   <si>
+    <t>额外盒子</t>
+  </si>
+  <si>
     <t>Jam3DShuffle</t>
   </si>
   <si>
@@ -122,24 +140,33 @@
     <t>Prop_Jam3DShuffle</t>
   </si>
   <si>
+    <t>洗牌</t>
+  </si>
+  <si>
+    <t>Jam3DRevert</t>
+  </si>
+  <si>
+    <t>icon_jam_2202</t>
+  </si>
+  <si>
+    <t>Prop_Jam3DReplace</t>
+  </si>
+  <si>
+    <t>还原</t>
+  </si>
+  <si>
     <t>Jam3DReplace</t>
   </si>
   <si>
-    <t>icon_jam_2202</t>
-  </si>
-  <si>
-    <t>Prop_Jam3DReplace</t>
-  </si>
-  <si>
-    <t>Jam3DRevert</t>
-  </si>
-  <si>
     <t>icon_jam_2203</t>
   </si>
   <si>
     <t>Prop_Jam3DRevert</t>
   </si>
   <si>
+    <t>待放等待</t>
+  </si>
+  <si>
     <t>TileRecall</t>
   </si>
   <si>
@@ -158,6 +185,9 @@
     <t>Prop_TileMagnet</t>
   </si>
   <si>
+    <t>磁体</t>
+  </si>
+  <si>
     <t>TileShuffle</t>
   </si>
   <si>
@@ -167,7 +197,7 @@
     <t>Prop_TileShuffle</t>
   </si>
   <si>
-    <t>BusCarshift</t>
+    <t>BusRefreshColor</t>
   </si>
   <si>
     <t>icon_bus_2401</t>
@@ -176,25 +206,34 @@
     <t>Prop_BusCarshift</t>
   </si>
   <si>
-    <t>BusChopper</t>
+    <t>刷新车颜色</t>
+  </si>
+  <si>
+    <t>BusVIPSpot</t>
   </si>
   <si>
     <t>icon_bus_2402</t>
   </si>
   <si>
+    <t>Prop_BusMinionshift</t>
+  </si>
+  <si>
+    <t>VIP车位</t>
+  </si>
+  <si>
+    <t>BusSortDepart</t>
+  </si>
+  <si>
+    <t>icon_bus_2403</t>
+  </si>
+  <si>
     <t>Prop_BusChopper</t>
   </si>
   <si>
-    <t>BusMinionshift</t>
-  </si>
-  <si>
-    <t>icon_bus_2403</t>
-  </si>
-  <si>
-    <t>Prop_BusMinionshift</t>
-  </si>
-  <si>
-    <t>BusAddspot</t>
+    <t>排序小人</t>
+  </si>
+  <si>
+    <t>BusExtraSpot</t>
   </si>
   <si>
     <t>icon_bus_2404</t>
@@ -203,6 +242,9 @@
     <t>Prop_BusAddspot</t>
   </si>
   <si>
+    <t>额外停车位</t>
+  </si>
+  <si>
     <t>TripleEraser</t>
   </si>
   <si>
@@ -212,16 +254,19 @@
     <t>Prop_TripleEraser</t>
   </si>
   <si>
-    <t>TripleRecall3</t>
+    <t>消除一组</t>
+  </si>
+  <si>
+    <t>TripleRevert</t>
   </si>
   <si>
     <t>icon_triple_2502</t>
   </si>
   <si>
-    <t>Prop_TripleRecall3</t>
-  </si>
-  <si>
-    <t>TripleCompass</t>
+    <t>Prop_TripleRecall</t>
+  </si>
+  <si>
+    <t>TripleHint</t>
   </si>
   <si>
     <t>icon_triple_2503</t>
@@ -230,13 +275,19 @@
     <t>Prop_TripleCompass</t>
   </si>
   <si>
-    <t>TripleHourglass</t>
+    <t>提示</t>
+  </si>
+  <si>
+    <t>TripleAddTime</t>
   </si>
   <si>
     <t>icon_triple_2504</t>
   </si>
   <si>
     <t>Prop_TripleHourglass</t>
+  </si>
+  <si>
+    <t>增加时间</t>
   </si>
 </sst>
 </file>
@@ -1243,8 +1294,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <dimension ref="A1:E26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="7.88333333333333" customWidth="1"/>
     <col min="2" max="2" width="16.825" customWidth="1"/>
@@ -1317,7 +1368,7 @@
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" ht="16.5" spans="1:4">
+    <row r="7" ht="16.5" spans="1:5">
       <c r="A7" s="2">
         <v>101</v>
       </c>
@@ -1330,271 +1381,331 @@
       <c r="D7" s="4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" ht="16.5" spans="1:4">
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" spans="1:5">
       <c r="A8" s="2">
         <v>102</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" ht="16.5" spans="1:4">
+        <v>16</v>
+      </c>
+      <c r="E8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" spans="1:5">
       <c r="A9" s="2">
         <v>103</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" ht="16.5" spans="1:4">
+        <v>20</v>
+      </c>
+      <c r="E9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" spans="1:5">
       <c r="A10" s="5">
         <v>2101</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:4">
+        <v>24</v>
+      </c>
+      <c r="E10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" spans="1:5">
       <c r="A11" s="5">
         <v>2102</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" ht="16.5" spans="1:4">
+        <v>28</v>
+      </c>
+      <c r="E11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" spans="1:5">
       <c r="A12" s="5">
         <v>2103</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" ht="16.5" spans="1:4">
+        <v>32</v>
+      </c>
+      <c r="E12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" spans="1:5">
       <c r="A13" s="7">
         <v>2201</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" ht="16.5" spans="1:4">
+        <v>36</v>
+      </c>
+      <c r="E13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" spans="1:5">
       <c r="A14" s="7">
         <v>2202</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" ht="16.5" spans="1:4">
+        <v>40</v>
+      </c>
+      <c r="E14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" spans="1:5">
       <c r="A15" s="7">
         <v>2203</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" ht="16.5" spans="1:4">
+        <v>44</v>
+      </c>
+      <c r="E15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" ht="16.5" spans="1:5">
       <c r="A16" s="5">
         <v>2301</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="17" ht="16.5" spans="1:4">
+        <v>48</v>
+      </c>
+      <c r="E16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" ht="16.5" spans="1:5">
       <c r="A17" s="5">
         <v>2302</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" ht="16.5" spans="1:4">
+        <v>51</v>
+      </c>
+      <c r="E17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" ht="16.5" spans="1:5">
       <c r="A18" s="5">
         <v>2303</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="19" ht="16.5" spans="1:4">
+        <v>55</v>
+      </c>
+      <c r="E18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" ht="16.5" spans="1:5">
       <c r="A19" s="7">
         <v>2401</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" ht="16.5" spans="1:4">
+        <v>58</v>
+      </c>
+      <c r="E19" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" ht="16.5" spans="1:5">
       <c r="A20" s="7">
         <v>2402</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="21" ht="16.5" spans="1:4">
+        <v>62</v>
+      </c>
+      <c r="E20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" ht="16.5" spans="1:5">
       <c r="A21" s="7">
         <v>2403</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="22" ht="16.5" spans="1:4">
+        <v>66</v>
+      </c>
+      <c r="E21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" ht="16.5" spans="1:5">
       <c r="A22" s="7">
         <v>2404</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="23" ht="16.5" spans="1:4">
+        <v>70</v>
+      </c>
+      <c r="E22" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" ht="16.5" spans="1:5">
       <c r="A23" s="5">
         <v>2501</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" ht="16.5" spans="1:4">
+        <v>74</v>
+      </c>
+      <c r="E23" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" ht="16.5" spans="1:5">
       <c r="A24" s="5">
         <v>2502</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="25" ht="16.5" spans="1:4">
+        <v>78</v>
+      </c>
+      <c r="E24" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" ht="16.5" spans="1:5">
       <c r="A25" s="5">
         <v>2503</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="26" ht="16.5" spans="1:4">
+        <v>81</v>
+      </c>
+      <c r="E25" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" ht="16.5" spans="1:5">
       <c r="A26" s="5">
         <v>2504</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>69</v>
+        <v>85</v>
+      </c>
+      <c r="E26" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/_OriginalData/Excel/Config/Common/Prop.xlsx
+++ b/Assets/_OriginalData/Excel/Config/Common/Prop.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" tabRatio="530"/>
+    <workbookView windowWidth="22800" windowHeight="9930" tabRatio="530"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="92">
   <si>
     <t>ID</t>
   </si>
@@ -38,6 +38,9 @@
     <t>图标</t>
   </si>
   <si>
+    <t>参数1</t>
+  </si>
+  <si>
     <t>多语言对应Key</t>
   </si>
   <si>
@@ -47,6 +50,9 @@
     <t>icon</t>
   </si>
   <si>
+    <t>param1</t>
+  </si>
+  <si>
     <t>nameTextKey</t>
   </si>
   <si>
@@ -257,6 +263,9 @@
     <t>消除一组</t>
   </si>
   <si>
+    <t>4个</t>
+  </si>
+  <si>
     <t>TripleRevert</t>
   </si>
   <si>
@@ -266,6 +275,9 @@
     <t>Prop_TripleRecall</t>
   </si>
   <si>
+    <t>3步</t>
+  </si>
+  <si>
     <t>TripleHint</t>
   </si>
   <si>
@@ -275,7 +287,7 @@
     <t>Prop_TripleCompass</t>
   </si>
   <si>
-    <t>提示</t>
+    <t>提示一组</t>
   </si>
   <si>
     <t>TripleAddTime</t>
@@ -288,6 +300,9 @@
   </si>
   <si>
     <t>增加时间</t>
+  </si>
+  <si>
+    <t>20s</t>
   </si>
 </sst>
 </file>
@@ -930,9 +945,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1294,19 +1312,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <dimension ref="A1:G26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="7.88333333333333" customWidth="1"/>
     <col min="2" max="2" width="16.825" customWidth="1"/>
     <col min="3" max="3" width="19.4083333333333" customWidth="1"/>
-    <col min="4" max="4" width="20.8666666666667" customWidth="1"/>
-    <col min="5" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="21.875" customWidth="1"/>
-    <col min="8" max="8" width="28.25" customWidth="1"/>
+    <col min="4" max="4" width="7.5" customWidth="1"/>
+    <col min="5" max="5" width="20.8666666666667" customWidth="1"/>
+    <col min="6" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="21.875" customWidth="1"/>
+    <col min="9" max="9" width="28.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:4">
+    <row r="1" ht="16.5" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1319,393 +1338,440 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:4">
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" ht="16.5" spans="1:4">
+      <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" ht="16.5" spans="1:5">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
-    </row>
-    <row r="4" ht="16.5" spans="1:4">
+      <c r="E3" s="1"/>
+    </row>
+    <row r="4" ht="16.5" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" ht="16.5" spans="1:4">
+        <v>10</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" ht="16.5" spans="1:5">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
-    </row>
-    <row r="6" ht="16.5" spans="1:4">
+      <c r="E5" s="1"/>
+    </row>
+    <row r="6" ht="16.5" spans="1:5">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
-    </row>
-    <row r="7" ht="16.5" spans="1:5">
-      <c r="A7" s="2">
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" ht="16.5" spans="1:6">
+      <c r="A7" s="3">
         <v>101</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="4" t="s">
+      <c r="B7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E7" t="s">
+      <c r="C7" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="8" ht="16.5" spans="1:5">
-      <c r="A8" s="2">
+      <c r="D7" s="4"/>
+      <c r="E7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" spans="1:6">
+      <c r="A8" s="3">
         <v>102</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="4" t="s">
+      <c r="B8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E8" t="s">
+      <c r="C8" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="9" ht="16.5" spans="1:5">
-      <c r="A9" s="2">
+      <c r="D8" s="4"/>
+      <c r="E8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" spans="1:6">
+      <c r="A9" s="3">
         <v>103</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E9" t="s">
+      <c r="C9" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="10" ht="16.5" spans="1:5">
-      <c r="A10" s="5">
+      <c r="D9" s="4"/>
+      <c r="E9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" spans="1:6">
+      <c r="A10" s="6">
         <v>2101</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="6" t="s">
+      <c r="B10" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E10" t="s">
+      <c r="C10" s="7" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:5">
-      <c r="A11" s="5">
+      <c r="D10" s="7"/>
+      <c r="E10" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" spans="1:6">
+      <c r="A11" s="6">
         <v>2102</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="6" t="s">
+      <c r="B11" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E11" t="s">
+      <c r="C11" s="7" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="12" ht="16.5" spans="1:5">
-      <c r="A12" s="5">
+      <c r="D11" s="7"/>
+      <c r="E11" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" spans="1:6">
+      <c r="A12" s="6">
         <v>2103</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" s="6" t="s">
+      <c r="B12" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E12" t="s">
+      <c r="C12" s="7" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="13" ht="16.5" spans="1:5">
-      <c r="A13" s="7">
+      <c r="D12" s="7"/>
+      <c r="E12" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" spans="1:6">
+      <c r="A13" s="8">
         <v>2201</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" s="8" t="s">
+      <c r="B13" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="E13" t="s">
+      <c r="C13" s="9" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="14" ht="16.5" spans="1:5">
-      <c r="A14" s="7">
+      <c r="D13" s="9"/>
+      <c r="E13" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" spans="1:6">
+      <c r="A14" s="8">
         <v>2202</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="C14" s="8" t="s">
+      <c r="B14" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" spans="1:6">
+      <c r="A15" s="8">
+        <v>2203</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" ht="16.5" spans="1:6">
+      <c r="A16" s="6">
+        <v>2301</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F16" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" ht="16.5" spans="1:6">
+      <c r="A17" s="6">
+        <v>2302</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" ht="16.5" spans="1:6">
+      <c r="A18" s="6">
+        <v>2303</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="F18" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E14" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" ht="16.5" spans="1:5">
-      <c r="A15" s="7">
-        <v>2203</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" s="8" t="s">
+    </row>
+    <row r="19" ht="16.5" spans="1:6">
+      <c r="A19" s="8">
+        <v>2401</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="F19" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" ht="16.5" spans="1:6">
+      <c r="A20" s="8">
+        <v>2402</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="F20" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" ht="16.5" spans="1:6">
+      <c r="A21" s="8">
+        <v>2403</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F21" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" ht="16.5" spans="1:6">
+      <c r="A22" s="8">
+        <v>2404</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="F22" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" ht="16.5" spans="1:7">
+      <c r="A23" s="6">
+        <v>2501</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D23" s="7">
+        <v>4</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="F23" t="s">
+        <v>77</v>
+      </c>
+      <c r="G23" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="24" ht="16.5" spans="1:7">
+      <c r="A24" s="6">
+        <v>2502</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D24" s="7">
+        <v>3</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F24" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E15" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" ht="16.5" spans="1:5">
-      <c r="A16" s="5">
-        <v>2301</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E16" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" ht="16.5" spans="1:5">
-      <c r="A17" s="5">
-        <v>2302</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="18" ht="16.5" spans="1:5">
-      <c r="A18" s="5">
-        <v>2303</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="E18" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="19" ht="16.5" spans="1:5">
-      <c r="A19" s="7">
-        <v>2401</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E19" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="20" ht="16.5" spans="1:5">
-      <c r="A20" s="7">
-        <v>2402</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="E20" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" ht="16.5" spans="1:5">
-      <c r="A21" s="7">
-        <v>2403</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E21" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="22" ht="16.5" spans="1:5">
-      <c r="A22" s="7">
-        <v>2404</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E22" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="23" ht="16.5" spans="1:5">
-      <c r="A23" s="5">
-        <v>2501</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E23" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="24" ht="16.5" spans="1:5">
-      <c r="A24" s="5">
-        <v>2502</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="E24" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="25" ht="16.5" spans="1:5">
-      <c r="A25" s="5">
+      <c r="G24" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="25" ht="16.5" spans="1:6">
+      <c r="A25" s="6">
         <v>2503</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="E25" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="26" ht="16.5" spans="1:5">
-      <c r="A26" s="5">
+      <c r="B25" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F25" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" ht="16.5" spans="1:7">
+      <c r="A26" s="6">
         <v>2504</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="E26" t="s">
-        <v>86</v>
+      <c r="B26" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D26" s="7">
+        <v>20</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="F26" t="s">
+        <v>90</v>
+      </c>
+      <c r="G26" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/_OriginalData/Excel/Config/Common/Prop.xlsx
+++ b/Assets/_OriginalData/Excel/Config/Common/Prop.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22800" windowHeight="9930" tabRatio="530"/>
+    <workbookView windowWidth="24720" windowHeight="11265" tabRatio="530"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1312,8 +1312,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <dimension ref="A1:I26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="7.88333333333333" customWidth="1"/>
     <col min="2" max="2" width="16.825" customWidth="1"/>
@@ -1321,8 +1321,8 @@
     <col min="4" max="4" width="7.5" customWidth="1"/>
     <col min="5" max="5" width="20.8666666666667" customWidth="1"/>
     <col min="6" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="21.875" customWidth="1"/>
-    <col min="9" max="9" width="28.25" customWidth="1"/>
+    <col min="8" max="8" width="16.15" customWidth="1"/>
+    <col min="9" max="9" width="8.74166666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:5">
@@ -1417,7 +1417,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" ht="16.5" spans="1:6">
+    <row r="8" ht="16.5" spans="1:9">
       <c r="A8" s="3">
         <v>102</v>
       </c>
@@ -1434,8 +1434,11 @@
       <c r="F8" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="9" ht="16.5" spans="1:6">
+      <c r="I8">
+        <v>19001</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" spans="1:9">
       <c r="A9" s="3">
         <v>103</v>
       </c>
@@ -1452,8 +1455,11 @@
       <c r="F9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="10" ht="16.5" spans="1:6">
+      <c r="I9">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" spans="1:9">
       <c r="A10" s="6">
         <v>2101</v>
       </c>
@@ -1470,8 +1476,11 @@
       <c r="F10" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:6">
+      <c r="I10">
+        <v>19036</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" spans="1:9">
       <c r="A11" s="6">
         <v>2102</v>
       </c>
@@ -1488,8 +1497,11 @@
       <c r="F11" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="12" ht="16.5" spans="1:6">
+      <c r="I11">
+        <v>19037</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" spans="1:9">
       <c r="A12" s="6">
         <v>2103</v>
       </c>
@@ -1506,8 +1518,11 @@
       <c r="F12" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="13" ht="16.5" spans="1:6">
+      <c r="I12">
+        <v>19038</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" spans="1:9">
       <c r="A13" s="8">
         <v>2201</v>
       </c>
@@ -1524,8 +1539,11 @@
       <c r="F13" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="14" ht="16.5" spans="1:6">
+      <c r="I13">
+        <v>19027</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" spans="1:9">
       <c r="A14" s="8">
         <v>2202</v>
       </c>
@@ -1542,8 +1560,11 @@
       <c r="F14" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="15" ht="16.5" spans="1:6">
+      <c r="I14">
+        <v>19029</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" spans="1:9">
       <c r="A15" s="8">
         <v>2203</v>
       </c>
@@ -1560,8 +1581,11 @@
       <c r="F15" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="16" ht="16.5" spans="1:6">
+      <c r="I15">
+        <v>19028</v>
+      </c>
+    </row>
+    <row r="16" ht="16.5" spans="1:9">
       <c r="A16" s="6">
         <v>2301</v>
       </c>
@@ -1578,8 +1602,11 @@
       <c r="F16" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="17" ht="16.5" spans="1:6">
+      <c r="I16">
+        <v>19002</v>
+      </c>
+    </row>
+    <row r="17" ht="16.5" spans="1:9">
       <c r="A17" s="6">
         <v>2302</v>
       </c>
@@ -1596,8 +1623,11 @@
       <c r="F17" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="18" ht="16.5" spans="1:6">
+      <c r="I17">
+        <v>19003</v>
+      </c>
+    </row>
+    <row r="18" ht="16.5" spans="1:9">
       <c r="A18" s="6">
         <v>2303</v>
       </c>
@@ -1614,8 +1644,11 @@
       <c r="F18" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="19" ht="16.5" spans="1:6">
+      <c r="I18">
+        <v>19004</v>
+      </c>
+    </row>
+    <row r="19" ht="16.5" spans="1:9">
       <c r="A19" s="8">
         <v>2401</v>
       </c>
@@ -1632,8 +1665,11 @@
       <c r="F19" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="20" ht="16.5" spans="1:6">
+      <c r="I19">
+        <v>19039</v>
+      </c>
+    </row>
+    <row r="20" ht="16.5" spans="1:9">
       <c r="A20" s="8">
         <v>2402</v>
       </c>
@@ -1650,8 +1686,11 @@
       <c r="F20" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="21" ht="16.5" spans="1:6">
+      <c r="I20">
+        <v>19041</v>
+      </c>
+    </row>
+    <row r="21" ht="16.5" spans="1:9">
       <c r="A21" s="8">
         <v>2403</v>
       </c>
@@ -1668,8 +1707,11 @@
       <c r="F21" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="22" ht="16.5" spans="1:6">
+      <c r="I21">
+        <v>19040</v>
+      </c>
+    </row>
+    <row r="22" ht="16.5" spans="1:9">
       <c r="A22" s="8">
         <v>2404</v>
       </c>
@@ -1686,8 +1728,11 @@
       <c r="F22" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="23" ht="16.5" spans="1:7">
+      <c r="I22">
+        <v>19042</v>
+      </c>
+    </row>
+    <row r="23" ht="16.5" spans="1:9">
       <c r="A23" s="6">
         <v>2501</v>
       </c>
@@ -1709,8 +1754,11 @@
       <c r="G23" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="24" ht="16.5" spans="1:7">
+      <c r="I23">
+        <v>19143</v>
+      </c>
+    </row>
+    <row r="24" ht="16.5" spans="1:9">
       <c r="A24" s="6">
         <v>2502</v>
       </c>
@@ -1732,8 +1780,11 @@
       <c r="G24" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="25" ht="16.5" spans="1:6">
+      <c r="I24">
+        <v>19144</v>
+      </c>
+    </row>
+    <row r="25" ht="16.5" spans="1:9">
       <c r="A25" s="6">
         <v>2503</v>
       </c>
@@ -1750,8 +1801,11 @@
       <c r="F25" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="26" ht="16.5" spans="1:7">
+      <c r="I25">
+        <v>19045</v>
+      </c>
+    </row>
+    <row r="26" ht="16.5" spans="1:9">
       <c r="A26" s="6">
         <v>2504</v>
       </c>
@@ -1772,6 +1826,9 @@
       </c>
       <c r="G26" t="s">
         <v>91</v>
+      </c>
+      <c r="I26">
+        <v>19146</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/_OriginalData/Excel/Config/Common/Prop.xlsx
+++ b/Assets/_OriginalData/Excel/Config/Common/Prop.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24720" windowHeight="11265" tabRatio="530"/>
+    <workbookView windowWidth="28020" windowHeight="11265" tabRatio="530"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,6 +26,471 @@
 </workbook>
 </file>
 
+<file path=xl/cellimages.xml><?xml version="1.0" encoding="utf-8"?>
+<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="ID_4BD3AA878E3B48F6B93BD94C884F1441" descr="icon_heart"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1625600" cy="1625600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="ID_BF121E495A924C9C81BAD750C6530409" descr="icon_screw_2101"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1955800" cy="1955800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="ID_24FEB584921A4827AA5E9DA269E99635" descr="icon_jam_2203"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1955800" cy="1955800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="24" name="ID_0254CAB0A0444BDE9711CB6F00184B94" descr="icon_coin"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1625600" cy="1625600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="25" name="ID_B63BBEDD626B4C73A3A0A03E1A905A35" descr="icon_screw_2102"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1955800" cy="1955800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="26" name="ID_7DA6758F91324D5FB4776157E63B4869" descr="icon_bus_2403"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1955800" cy="1955800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="27" name="ID_13A0107700F6443EAA7AF464C52F9082" descr="icon_screw_2103"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1955800" cy="1955800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="28" name="ID_0723869AC903431F9D1FC3DA84F32317" descr="icon_jam_2201"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1955800" cy="1955800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="29" name="ID_EE02EA6CCF23457581CB013586798B89" descr="icon_jam_2202"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1955800" cy="1955800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="30" name="ID_2BB00A3DB7464BBA837A10CFCEB9E08C" descr="icon_tile_2301"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1955800" cy="1955800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="31" name="ID_90A479472AD44331B13F975A97AEBCCE" descr="icon_tile_2302"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1955800" cy="1955800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="32" name="ID_A769F0FA36A44F27941DDF4FDEDD39DF" descr="icon_tile_2303"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1955800" cy="1955800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="33" name="ID_C6412C55AEED4910A919D76DAA7D0BF9" descr="icon_bus_2401"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1955800" cy="1955800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="34" name="ID_1DF6ECC57BBD4D02ADC849FC318A96BF" descr="icon_triple_2502"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1955800" cy="1955800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="35" name="ID_070B7AB1FBB74D97A541DEE15B57EFC9" descr="icon_bus_2402"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1955800" cy="1955800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="36" name="ID_9AE4948B03A44B09AE2354A82C9F0826" descr="icon_bus_2404"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1955800" cy="1955800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="37" name="ID_16F2BC7B538B450384FA4A491076C5C5" descr="icon_triple_2501"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1955800" cy="1955800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="38" name="ID_0D87E80D4FB84FADAF45487C47F9014F" descr="icon_triple_2503"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1955800" cy="1955800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="39" name="ID_7936E73D497048A1B2F2F211555D1F87" descr="icon_triple_2504"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId19"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1955800" cy="1955800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="40" name="ID_8A86D14AFADF4DDFB4F05315BDE79CAC" descr="icon_noads"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId20"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1625600" cy="1625600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+</etc:cellImages>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="92">
   <si>
@@ -315,7 +780,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -333,6 +798,13 @@
       <sz val="11"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -815,137 +1287,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -964,6 +1436,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1312,7 +1787,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="7.88333333333333" customWidth="1"/>
@@ -1320,9 +1795,11 @@
     <col min="3" max="3" width="19.4083333333333" customWidth="1"/>
     <col min="4" max="4" width="7.5" customWidth="1"/>
     <col min="5" max="5" width="20.8666666666667" customWidth="1"/>
-    <col min="6" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="16.15" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="9.03333333333333" customWidth="1"/>
+    <col min="8" max="8" width="9.99166666666667" customWidth="1"/>
     <col min="9" max="9" width="8.74166666666667" customWidth="1"/>
+    <col min="10" max="10" width="6.63333333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:5">
@@ -1399,7 +1876,7 @@
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
     </row>
-    <row r="7" ht="16.5" spans="1:6">
+    <row r="7" ht="20" customHeight="1" spans="1:10">
       <c r="A7" s="3">
         <v>101</v>
       </c>
@@ -1416,8 +1893,12 @@
       <c r="F7" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" ht="16.5" spans="1:9">
+      <c r="J7" s="10" t="str">
+        <f>_xlfn.DISPIMG("ID_8A86D14AFADF4DDFB4F05315BDE79CAC",1)</f>
+        <v>=DISPIMG("ID_8A86D14AFADF4DDFB4F05315BDE79CAC",1)</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1" spans="1:10">
       <c r="A8" s="3">
         <v>102</v>
       </c>
@@ -1437,8 +1918,12 @@
       <c r="I8">
         <v>19001</v>
       </c>
-    </row>
-    <row r="9" ht="16.5" spans="1:9">
+      <c r="J8" s="10" t="str">
+        <f>_xlfn.DISPIMG("ID_4BD3AA878E3B48F6B93BD94C884F1441",1)</f>
+        <v>=DISPIMG("ID_4BD3AA878E3B48F6B93BD94C884F1441",1)</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1" spans="1:10">
       <c r="A9" s="3">
         <v>103</v>
       </c>
@@ -1458,8 +1943,12 @@
       <c r="I9">
         <v>10010</v>
       </c>
-    </row>
-    <row r="10" ht="16.5" spans="1:9">
+      <c r="J9" s="10" t="str">
+        <f>_xlfn.DISPIMG("ID_0254CAB0A0444BDE9711CB6F00184B94",1)</f>
+        <v>=DISPIMG("ID_0254CAB0A0444BDE9711CB6F00184B94",1)</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1" spans="1:10">
       <c r="A10" s="6">
         <v>2101</v>
       </c>
@@ -1479,8 +1968,12 @@
       <c r="I10">
         <v>19036</v>
       </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:9">
+      <c r="J10" s="10" t="str">
+        <f>_xlfn.DISPIMG("ID_BF121E495A924C9C81BAD750C6530409",1)</f>
+        <v>=DISPIMG("ID_BF121E495A924C9C81BAD750C6530409",1)</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1" spans="1:10">
       <c r="A11" s="6">
         <v>2102</v>
       </c>
@@ -1500,8 +1993,12 @@
       <c r="I11">
         <v>19037</v>
       </c>
-    </row>
-    <row r="12" ht="16.5" spans="1:9">
+      <c r="J11" s="10" t="str">
+        <f>_xlfn.DISPIMG("ID_B63BBEDD626B4C73A3A0A03E1A905A35",1)</f>
+        <v>=DISPIMG("ID_B63BBEDD626B4C73A3A0A03E1A905A35",1)</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1" spans="1:10">
       <c r="A12" s="6">
         <v>2103</v>
       </c>
@@ -1521,8 +2018,12 @@
       <c r="I12">
         <v>19038</v>
       </c>
-    </row>
-    <row r="13" ht="16.5" spans="1:9">
+      <c r="J12" s="10" t="str">
+        <f>_xlfn.DISPIMG("ID_13A0107700F6443EAA7AF464C52F9082",1)</f>
+        <v>=DISPIMG("ID_13A0107700F6443EAA7AF464C52F9082",1)</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1" spans="1:10">
       <c r="A13" s="8">
         <v>2201</v>
       </c>
@@ -1542,8 +2043,12 @@
       <c r="I13">
         <v>19027</v>
       </c>
-    </row>
-    <row r="14" ht="16.5" spans="1:9">
+      <c r="J13" s="10" t="str">
+        <f>_xlfn.DISPIMG("ID_0723869AC903431F9D1FC3DA84F32317",1)</f>
+        <v>=DISPIMG("ID_0723869AC903431F9D1FC3DA84F32317",1)</v>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1" spans="1:10">
       <c r="A14" s="8">
         <v>2202</v>
       </c>
@@ -1563,8 +2068,12 @@
       <c r="I14">
         <v>19029</v>
       </c>
-    </row>
-    <row r="15" ht="16.5" spans="1:9">
+      <c r="J14" s="10" t="str">
+        <f>_xlfn.DISPIMG("ID_EE02EA6CCF23457581CB013586798B89",1)</f>
+        <v>=DISPIMG("ID_EE02EA6CCF23457581CB013586798B89",1)</v>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1" spans="1:10">
       <c r="A15" s="8">
         <v>2203</v>
       </c>
@@ -1584,8 +2093,12 @@
       <c r="I15">
         <v>19028</v>
       </c>
-    </row>
-    <row r="16" ht="16.5" spans="1:9">
+      <c r="J15" s="10" t="str">
+        <f>_xlfn.DISPIMG("ID_24FEB584921A4827AA5E9DA269E99635",1)</f>
+        <v>=DISPIMG("ID_24FEB584921A4827AA5E9DA269E99635",1)</v>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1" spans="1:10">
       <c r="A16" s="6">
         <v>2301</v>
       </c>
@@ -1605,8 +2118,12 @@
       <c r="I16">
         <v>19002</v>
       </c>
-    </row>
-    <row r="17" ht="16.5" spans="1:9">
+      <c r="J16" s="10" t="str">
+        <f>_xlfn.DISPIMG("ID_2BB00A3DB7464BBA837A10CFCEB9E08C",1)</f>
+        <v>=DISPIMG("ID_2BB00A3DB7464BBA837A10CFCEB9E08C",1)</v>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1" spans="1:10">
       <c r="A17" s="6">
         <v>2302</v>
       </c>
@@ -1626,8 +2143,12 @@
       <c r="I17">
         <v>19003</v>
       </c>
-    </row>
-    <row r="18" ht="16.5" spans="1:9">
+      <c r="J17" s="10" t="str">
+        <f>_xlfn.DISPIMG("ID_90A479472AD44331B13F975A97AEBCCE",1)</f>
+        <v>=DISPIMG("ID_90A479472AD44331B13F975A97AEBCCE",1)</v>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1" spans="1:10">
       <c r="A18" s="6">
         <v>2303</v>
       </c>
@@ -1647,8 +2168,12 @@
       <c r="I18">
         <v>19004</v>
       </c>
-    </row>
-    <row r="19" ht="16.5" spans="1:9">
+      <c r="J18" s="10" t="str">
+        <f>_xlfn.DISPIMG("ID_A769F0FA36A44F27941DDF4FDEDD39DF",1)</f>
+        <v>=DISPIMG("ID_A769F0FA36A44F27941DDF4FDEDD39DF",1)</v>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1" spans="1:10">
       <c r="A19" s="8">
         <v>2401</v>
       </c>
@@ -1668,8 +2193,12 @@
       <c r="I19">
         <v>19039</v>
       </c>
-    </row>
-    <row r="20" ht="16.5" spans="1:9">
+      <c r="J19" s="10" t="str">
+        <f>_xlfn.DISPIMG("ID_C6412C55AEED4910A919D76DAA7D0BF9",1)</f>
+        <v>=DISPIMG("ID_C6412C55AEED4910A919D76DAA7D0BF9",1)</v>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1" spans="1:10">
       <c r="A20" s="8">
         <v>2402</v>
       </c>
@@ -1689,8 +2218,12 @@
       <c r="I20">
         <v>19041</v>
       </c>
-    </row>
-    <row r="21" ht="16.5" spans="1:9">
+      <c r="J20" s="10" t="str">
+        <f>_xlfn.DISPIMG("ID_070B7AB1FBB74D97A541DEE15B57EFC9",1)</f>
+        <v>=DISPIMG("ID_070B7AB1FBB74D97A541DEE15B57EFC9",1)</v>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1" spans="1:10">
       <c r="A21" s="8">
         <v>2403</v>
       </c>
@@ -1710,8 +2243,12 @@
       <c r="I21">
         <v>19040</v>
       </c>
-    </row>
-    <row r="22" ht="16.5" spans="1:9">
+      <c r="J21" s="10" t="str">
+        <f>_xlfn.DISPIMG("ID_7DA6758F91324D5FB4776157E63B4869",1)</f>
+        <v>=DISPIMG("ID_7DA6758F91324D5FB4776157E63B4869",1)</v>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1" spans="1:10">
       <c r="A22" s="8">
         <v>2404</v>
       </c>
@@ -1731,8 +2268,12 @@
       <c r="I22">
         <v>19042</v>
       </c>
-    </row>
-    <row r="23" ht="16.5" spans="1:9">
+      <c r="J22" s="10" t="str">
+        <f>_xlfn.DISPIMG("ID_9AE4948B03A44B09AE2354A82C9F0826",1)</f>
+        <v>=DISPIMG("ID_9AE4948B03A44B09AE2354A82C9F0826",1)</v>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1" spans="1:10">
       <c r="A23" s="6">
         <v>2501</v>
       </c>
@@ -1757,8 +2298,12 @@
       <c r="I23">
         <v>19143</v>
       </c>
-    </row>
-    <row r="24" ht="16.5" spans="1:9">
+      <c r="J23" s="10" t="str">
+        <f>_xlfn.DISPIMG("ID_16F2BC7B538B450384FA4A491076C5C5",1)</f>
+        <v>=DISPIMG("ID_16F2BC7B538B450384FA4A491076C5C5",1)</v>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1" spans="1:10">
       <c r="A24" s="6">
         <v>2502</v>
       </c>
@@ -1783,8 +2328,12 @@
       <c r="I24">
         <v>19144</v>
       </c>
-    </row>
-    <row r="25" ht="16.5" spans="1:9">
+      <c r="J24" s="10" t="str">
+        <f>_xlfn.DISPIMG("ID_1DF6ECC57BBD4D02ADC849FC318A96BF",1)</f>
+        <v>=DISPIMG("ID_1DF6ECC57BBD4D02ADC849FC318A96BF",1)</v>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1" spans="1:10">
       <c r="A25" s="6">
         <v>2503</v>
       </c>
@@ -1804,8 +2353,12 @@
       <c r="I25">
         <v>19045</v>
       </c>
-    </row>
-    <row r="26" ht="16.5" spans="1:9">
+      <c r="J25" s="10" t="str">
+        <f>_xlfn.DISPIMG("ID_0D87E80D4FB84FADAF45487C47F9014F",1)</f>
+        <v>=DISPIMG("ID_0D87E80D4FB84FADAF45487C47F9014F",1)</v>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1" spans="1:10">
       <c r="A26" s="6">
         <v>2504</v>
       </c>
@@ -1829,6 +2382,10 @@
       </c>
       <c r="I26">
         <v>19146</v>
+      </c>
+      <c r="J26" s="10" t="str">
+        <f>_xlfn.DISPIMG("ID_7936E73D497048A1B2F2F211555D1F87",1)</f>
+        <v>=DISPIMG("ID_7936E73D497048A1B2F2F211555D1F87",1)</v>
       </c>
     </row>
   </sheetData>
